--- a/Result/checksun_type/電視.xlsx
+++ b/Result/checksun_type/電視.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,21 +1057,17 @@
           <t>24.94</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>25.12</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AM2" t="n">
+        <v>25.12</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>25.18</v>
+      </c>
+      <c r="AO2" t="inlineStr">
         <is>
           <t>25.18</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>25.18</t>
-        </is>
-      </c>
       <c r="AP2" t="inlineStr">
         <is>
           <t>-13.47</t>
@@ -1112,20 +1108,16 @@
           <t>790.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>1554.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>1554.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>2834.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>1995.22</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>1995.22</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-191.9349957355732</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>790</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>790.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,21 +1487,17 @@
           <t>24.93</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>25.12</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AM3" t="n">
+        <v>25.12</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>25.18</v>
+      </c>
+      <c r="AO3" t="inlineStr">
         <is>
           <t>25.18</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>25.18</t>
-        </is>
-      </c>
       <c r="AP3" t="inlineStr">
         <is>
           <t>-46.28</t>
@@ -1548,20 +1538,16 @@
           <t>340.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>1546.0</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>1546</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>2954.5</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>2043.08</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>2043.08</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-96.33445250818659</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>340</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>340.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>24.94</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>25.12</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>25.18</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>25.12</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>25.18</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>3851.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>2091.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>2091.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>3081.8</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>2105.04</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>2105.04</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>91.89255397765874</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>3851</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>3851.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,21 +2347,17 @@
           <t>25.01</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>25.14</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AM5" t="n">
+        <v>25.14</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>25.19</v>
+      </c>
+      <c r="AO5" t="inlineStr">
         <is>
           <t>25.19</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>25.19</t>
-        </is>
-      </c>
       <c r="AP5" t="inlineStr">
         <is>
           <t>-104.13</t>
@@ -2420,20 +2398,16 @@
           <t>1128.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>2644.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>2644.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>2844.9</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>2067.12</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>2067.12</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-18.67217082747857</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>1128</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>1128.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>25.12</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>25.16</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>25.21</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>25.16</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>25.21</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>1662.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>3717.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>3717.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>2854.1</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>2079.58</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>2079.58</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>115.7950855518779</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>1662</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>1662.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>25.17</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>25.18</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>25.22</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>25.18</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>25.22</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>749.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>4114.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>4114.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>2851.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>2099.22</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>2099.22</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>246.5413416098199</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>749</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>749.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>25.18</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>25.18</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>25.23</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>25.18</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>25.23</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>3068.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>4363.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>4363</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>2893.7</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>2113.1</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>2113.1</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>522.3380880636719</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>3068</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>3068.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>25.15</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>25.24</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>25.24</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>6615.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>4072.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>4072</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>2738.2</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>2098.46</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>2098.46</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>649.2142227097579</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>6615</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>6615.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,21 +4497,17 @@
           <t>25.16</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AM10" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="AO10" t="inlineStr">
         <is>
           <t>25.2</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>25.25</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
       <c r="AP10" t="inlineStr">
         <is>
           <t>29.54</t>
@@ -4600,20 +4548,16 @@
           <t>6495.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>3045.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>3045.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>2300.5</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>2001.88</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>2001.88</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>427.2439071073895</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>6495</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>6495.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>25.13</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>25.25</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>25.25</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>3645.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>1990.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>1990.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>1765.1</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>1920.52</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>1920.52</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>107.7418881358849</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>3645</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>3645.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>25.19</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>25.26</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>25.26</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>1992.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>1588.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>1588.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>1522.0</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>1896.0</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>1896</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-47.18034925683151</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>1992</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>1992.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>23.57</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>23.8</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>24.98</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>24.98</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>595.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>590.4</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>590.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>680.5</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>1093.86</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>1093.86</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-99.31783420592717</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>595</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>595.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>23.5</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>23.84</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>25.02</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>25.02</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>200.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>598.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>598.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>697.4</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>1116.88</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>1116.88</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-103.9491901489453</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>200</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>23.5</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>23.92</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>25.08</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>25.08</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>1074.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>734.4</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>734.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>847.1</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>1147.04</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>1147.04</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-64.53151327650903</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>1074</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>1074.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>23.52</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>23.99</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>25.15</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>25.15</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>861.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>619.8</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>619.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>860.0</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>1147.18</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>1147.18</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-99.55870655601029</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>861</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>861.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>23.57</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>24.05</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>25.21</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>25.21</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>222.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>624.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>624.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>891.2</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>1151.52</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>1151.52</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-123.2204574354405</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>222</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>222.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>23.56</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>24.1</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>25.28</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>25.28</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>635.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>770.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>770.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>1122.7</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>1161.18</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>1161.18</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-84.15794235478916</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>635</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>635.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>23.59</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>24.18</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>25.35</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>25.35</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>880.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>796.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>796.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>1113.6</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>1163.82</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>1163.82</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-69.59870858404474</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>880</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>880.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>23.59</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>24.25</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>25.42</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>25.42</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>501.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>959.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>959.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>1034.7</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>1174.78</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>1174.78</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-72.56413503355122</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>501</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>501.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>23.61</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>24.33</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>25.49</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>24.33</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>25.49</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>883.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>1100.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>1100.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>1009.7</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>1196.5</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>1196.5</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-33.60173942450501</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>883</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>883.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>23.64</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>24.39</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>25.56</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>24.39</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>25.56</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>954.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>1158.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>1158.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>1015.7</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>1195.92</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>1195.92</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-17.66968357499263</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>954</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>954.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>23.72</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>24.45</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>25.63</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>25.63</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>764.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>1474.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>1474.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>1128.2</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>1208.52</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>1208.52</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-1.885686519439332</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>764</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>764.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>14.61</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>14.48</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>14.4</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>14.4</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>24936838.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>30822043.8</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>30822043.8</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>46911445.1</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>51199805.14</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>51199805.14</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-3733685.064264968</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>24936838</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>24936838.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>14.6</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>14.46</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>14.37</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>14.37</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>20889696.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>36972173.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>36972173.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>49665121.5</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>51154306.6</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>51154306.6</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-2966680.800394706</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>20889696</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>20889696.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>14.72</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>14.47</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>14.34</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>14.34</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>40243435.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>45102521.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>45102521.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>51152191.4</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>51161794.86</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>51161794.86</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-1331385.180565961</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>40243435</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>40243435.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>14.88</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>14.5</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>14.33</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>14.33</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>35613427.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>44406342.4</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>44406342.4</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>50606982.4</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>50966314.28</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>50966314.28</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-1021314.002933256</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>35613427</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>35613427.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>14.98</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>14.55</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>14.31</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>14.31</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>32426823.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>46111197.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>46111197</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>51294892.3</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>50812570.52</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>50812570.52</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-45807.39192461967</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>32426823</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>32426823.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>15.1</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>14.59</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>14.3</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>14.3</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>55687485.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>63000846.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>63000846.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>51963178.8</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>50792076.3</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>50792076.3</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>1690831.316370726</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>55687485</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>55687485.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>15.08</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>14.62</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>14.28</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>14.28</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>61541437.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>62358069.8</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>62358069.8</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>48454781.8</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>51591368.42</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>51591368.42</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>1619143.138350844</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>61541437</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>61541437.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>14.88</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>14.62</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>14.24</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>14.24</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>36762540.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>57201861.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>57201861.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>45697674.1</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>50766311.38</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>50766311.38</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>831695.7719527707</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>36762540</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>36762540.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>14.66</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>14.63</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>14.21</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>14.21</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>44137700.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>56807622.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>56807622.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>44049880.7</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>50729203.92</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>50729203.92</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>2331949.363814346</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>44137700</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>44137700.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>14.38</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>14.63</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>14.17</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>14.17</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>116875070.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>56478587.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>56478587.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>42013498.2</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>50276522.96</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>50276522.96</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>3601689.160623237</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>116875070</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>116875070.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>14.15</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>14.63</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>14.13</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>14.13</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>52473602.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>40925511.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>40925511.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>34675123.2</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>48640844.18</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>48640844.18</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-2506318.242529176</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>52473602</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>52473602.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>32.36</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>33.57</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>36.62</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>33.57</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>36.62</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>403535423.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>568945866.2</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>568945866.2</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>551325175.1</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>652100733.04</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>652100733.04</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-64629376.5640012</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>403535423</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>403535423.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>32.41</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>33.75</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>36.78</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>36.78</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>363440217.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>575528949.6</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>575528949.6</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>594264436.4</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>657290966.96</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>657290966.96</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-58722927.5542357</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>363440217</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>363440217.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>32.3</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>33.94</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>36.93</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>33.94</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>36.93</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>451484020.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>575978704.8</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>575978704.8</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>641378457.8</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>656768454.26</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>656768454.26</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-43891980.91334808</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>451484020</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>451484020.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>32.09</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>34.14</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>37.07</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>34.14</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>37.07</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>569640781.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>620997783.6</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>620997783.6</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>705807978.8</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>655783883.94</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>655783883.9400001</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-30570608.14374614</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>569640781</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>569640781.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>32.14</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>34.4</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>37.2</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>37.2</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>1056628890.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>631631786.8</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>631631786.8</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>709807982.0</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>651233510.34</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>651233510.34</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-23107921.14632392</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>1056628890</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>1056628890.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>32.12</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>34.62</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>37.31</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>34.62</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>37.31</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>436450840.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>533704484.0</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>533704484</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>667262298.9</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>638216857.76</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>638216857.76</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-63798954.21620893</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>436450840</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>436450840.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>32.35</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>34.95</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>37.46</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>37.46</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>365688993.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>612999923.2</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>612999923.2</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>705359369.1</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>635887126.76</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>635887126.76</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-53202819.16546595</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>365688993</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>365688993.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>32.81</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>35.28</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>37.61</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>37.61</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>676579414.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>706778210.8</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>706778210.8</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>768838281.6</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>633235828.68</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>633235828.6799999</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-28583756.22992349</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>676579414</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>676579414.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>33.39</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>35.56</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>37.76</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>37.76</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>622810797.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>790618174.0</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>790618174</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>763691422.1</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>627286041.56</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>627286041.5599999</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-25702505.84950864</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>622810797</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>622810797.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>34.07</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>35.84</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>37.9</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>37.9</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>566992376.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>787984177.2</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>787984177.2</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>817890552.4</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>622376486.36</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>622376486.36</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-14907563.99000478</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>566992376</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>566992376.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>34.47</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>36.09</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>38.03</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>36.09</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>38.03</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>832928036.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>800820113.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>800820113.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>848956198.4</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>625070436.22</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>625070436.22</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>7026739.630357981</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>832928036</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>832928036.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>29.16</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>30.76</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>31.83</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>30.76</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>31.83</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>719006309.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>949851822.4</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>949851822.4</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>1034336783.1</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>1943240864.16</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>1943240864.16</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-130458949.546433</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>719006309</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>719006309.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>29.14</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>31.02</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>31.8</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>31.02</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>31.8</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>667847761.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>1067800185.6</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>1067800185.6</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>1021273105.5</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>1938830373.0</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>1938830373</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-121533602.5249245</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>667847761</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>667847761.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>31.26</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>31.77</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>31.77</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>1201959271.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>1180457053.0</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>1180457053</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>1068520962.5</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>1938375533.6</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>1938375533.6</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-98961347.97545075</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>1201959271</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>1201959271.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>29.03</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>31.59</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>31.76</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>31.76</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>1119253658.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>1129061877.8</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>1129061877.8</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>1010725999.7</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>1921840103.86</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>1921840103.86</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-120407169.4056509</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>1119253658</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>1119253658.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>29.27999999999999</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>31.9</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>31.75</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>31.75</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>1041192113.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>1105345654.0</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>1105345654</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>978154218.3</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>1906340616.66</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>1906340616.66</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-137882485.4343059</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>1041192113</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>1041192113.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>29.53</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>32.23</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>31.72</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>32.23</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>31.72</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>1308748125.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>1118821743.8</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>1118821743.8</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>936141852.9</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>1892720250.14</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>1892720250.14</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-149559111.1740165</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>1308748125</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>1308748125.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>29.82</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>32.48</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>31.69</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>32.48</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>31.69</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>1231132098.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>974746025.4</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>974746025.4</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>901408156.9</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>1876762391.38</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>1876762391.38</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-189565323.8316743</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>1231132098</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>1231132098.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>30.22</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>32.69</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>31.66</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>32.69</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>31.66</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>944983395.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>956584872.0</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>956584872</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>919270819.4</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>1860013080.08</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>1860013080.08</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-231630863.170054</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>944983395</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>944983395.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>30.72</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>32.9</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>31.62</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>31.62</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>1000672539.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>892390121.6</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>892390121.6</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>905448004.3</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>1847387257.46</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>1847387257.46</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-252793170.361666</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>1000672539</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>1000672539.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>31.07</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>31.56</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>33</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>31.56</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>1108572562.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>850962782.6</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>850962782.6</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>944921985.7</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>1839319197.86</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>1839319197.86</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-279963404.2653377</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>1108572562</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>1108572562.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>31.44</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>31.5</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>33.05</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>31.5</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>588369533.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>753461962.0</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>753461962</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>1014121978.2</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>1826207989.06</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>1826207989.06</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-320340047.8682499</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>588369533</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>588369533.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>34.14</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>34.28</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>35.67</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>34.28</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>35.67</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>703729.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>832338.4</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>832338.4</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>1365486.3</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>2770195.72</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>2770195.72</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-407242.1677682393</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>703729</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>703729.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>34.05</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>34.34</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>35.73</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>34.34</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>35.73</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>811272.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>1025107.0</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>1025107</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>1422951.5</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>2781982.36</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>2781982.36</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-397836.2898797004</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>811272</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>811272.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>33.98</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>34.42</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>35.78</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>34.42</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>35.78</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>1487179.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>1339575.6</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>1339575.6</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>1890505.4</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>2785701.92</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>2785701.92</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-381713.3468289413</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>1487179</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>1487179.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>33.97</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>34.5</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>35.84</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>35.84</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>582054.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>1655590.0</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>1655590</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>2092838.2</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>2769787.1</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>2769787.1</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-417466.5586553942</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>582054</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>582054.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>33.92999999999999</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>34.57</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>35.9</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>34.57</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>35.9</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>577458.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>1688519.2</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>1688519.2</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>2334206.6</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>2765629.48</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>2765629.48</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-356655.3770269202</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>577458</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>577458.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>33.93</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>34.66</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>35.97</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>35.97</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>1667572.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>1898634.2</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>1898634.2</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>2466923.8</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>2771121.32</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>2771121.32</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-256552.1398067102</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>1667572</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>1667572.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>33.97</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>34.74</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>36.03</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>34.74</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>36.03</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>2383615.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>1820796.0</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>1820796</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>2506266.8</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>2754839.88</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>2754839.88</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-221182.8673561704</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>2383615</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>2383615.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>33.98999999999999</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>34.83</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>36.09</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>34.83</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>36.09</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>3067251.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>2441435.2</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>2441435.2</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>2486763.3</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>2745284.78</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>2745284.78</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-239474.8400212508</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>3067251</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>3067251.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>33.98999999999999</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>34.92</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>36.15</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>36.15</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>746700.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>2530086.4</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>2530086.4</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>2848651.5</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>2788241.7</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>2788241.7</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-330300.2709706062</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>746700</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>746700.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>34.08</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>35.03</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>36.21</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>35.03</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>36.21</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>1628033.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>2979894.0</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>2979894</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>3115544.6</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>2857333.8</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>2857333.8</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-199623.9840778778</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>1628033</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>1628033.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>34.17</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>35.12</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>36.27</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>35.12</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>36.27</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>1278381.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>3035213.4</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>3035213.4</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>3208352.2</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>2902801.48</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>2902801.48</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-100242.6819426282</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>1278381</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>1278381.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>24.58</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>24.63</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>24.74</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>24.63</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>24.74</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>1755895.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>1971741.0</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>1971741</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>3427538.6</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>4252931.84</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>4252931.84</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-400046.7610960035</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>1755895</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>1755895.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>24.51</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>24.63</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>24.74</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>24.63</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>24.74</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>684413.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>2179519.6</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>2179519.6</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>3572620.7</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>4280187.1</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>4280187.1</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-347587.7031393521</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>684413</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>684413.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>24.46</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>24.64</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>24.74</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>24.74</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>4106411.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>4136138.2</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>4136138.2</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>3754690.3</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>4326768.72</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>4326768.72</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-145430.7023748737</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>4106411</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>4106411.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>24.46</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>24.64</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>24.74</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>24.74</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>2101052.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>3802575.2</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>3802575.2</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>3610120.3</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>4295272.64</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>4295272.64</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-218083.6761979447</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>2101052</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>2101052.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>24.54</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>24.66</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>24.75</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>24.66</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>24.75</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>1210934.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>4496822.2</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>4496822.2</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>3827327.8</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>4320361.0</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>4320361</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-99225.04322383273</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>1210934</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>1210934.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>24.6</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>24.68</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>24.75</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>24.68</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>24.75</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>2794788.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>4883336.2</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>4883336.2</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>3876114.4</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>4361348.24</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>4361348.24</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>169486.5411400348</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>2794788</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>2794788.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>24.68</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>24.71</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>24.76</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>24.76</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>10467506.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>4965721.8</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>4965721.8</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>4025537.8</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>4381655.3</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>4381655.3</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>377608.4994762735</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>10467506</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>10467506.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>24.75</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>24.74</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>24.76</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>24.74</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>24.76</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>2438596.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>3373242.4</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>3373242.4</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>3278879.7</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>4215534.16</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>4215534.16</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>-160637.3635961106</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>2438596</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>2438596.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>24.74</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>24.74</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>24.76</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>24.74</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>24.76</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>5572287.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>3417665.4</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>3417665.4</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>3954630.1</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>4246455.74</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>4246455.74</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>-63582.61928536929</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>5572287</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>5572287.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>24.73</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>24.74</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>24.75</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>24.74</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>24.75</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>3143504.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>3157833.4</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>3157833.4</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>3720514.4</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>4257394.12</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>4257394.12</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>-258414.7838669755</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>3143504</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>3143504.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>24.71</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>24.74</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>24.75</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>24.74</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>24.75</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>3206716.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>2868892.6</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>2868892.6</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>4187915.8</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>4233802.74</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>4233802.74</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>-267290.598131164</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>3206716</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>3206716.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
